--- a/artfynd/A 15760-2026 artfynd.xlsx
+++ b/artfynd/A 15760-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81754016</v>
+        <v>79781427</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91683</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>5678</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Kruskantarell</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Craterellus undulatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Campo &amp; Papetti</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norra Boarp, Sm</t>
+          <t>N om N boarp, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469145.8312091649</v>
+        <v>469459</v>
       </c>
       <c r="R2" t="n">
-        <v>6431083.082882264</v>
+        <v>6431165</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-01-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-01-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,33 +757,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kajsa Mattsson</t>
+          <t>Marcus Vestlund</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kajsa Mattsson, Tor Hansson Frank</t>
+          <t>Marcus Vestlund, Åke Bruhn, Hilda Mikaelsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>81754015</v>
+        <v>81754010</v>
       </c>
       <c r="B3" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -835,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469152.8979032536</v>
+        <v>469094</v>
       </c>
       <c r="R3" t="n">
-        <v>6431104.746217982</v>
+        <v>6430937</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,19 +848,9 @@
           <t>2019-01-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-01-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>81753924</v>
+        <v>81754011</v>
       </c>
       <c r="B4" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223246</v>
+        <v>220785</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -951,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469121.0306387788</v>
+        <v>469152</v>
       </c>
       <c r="R4" t="n">
-        <v>6431032.95214</v>
+        <v>6431093</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,24 +949,9 @@
           <t>2019-01-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-01-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Öster om E4</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>81754014</v>
+        <v>81754012</v>
       </c>
       <c r="B5" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1072,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469150.7629189456</v>
+        <v>469145</v>
       </c>
       <c r="R5" t="n">
-        <v>6431103.173607474</v>
+        <v>6431094</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,19 +1050,9 @@
           <t>2019-01-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-01-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>81754021</v>
+        <v>81754013</v>
       </c>
       <c r="B6" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>469164.0543543759</v>
+        <v>469149</v>
       </c>
       <c r="R6" t="n">
-        <v>6431106.249102163</v>
+        <v>6431095</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,19 +1151,9 @@
           <t>2019-01-28</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-01-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>81754017</v>
+        <v>81754014</v>
       </c>
       <c r="B7" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,10 +1219,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>469149.0603229101</v>
+        <v>469151</v>
       </c>
       <c r="R7" t="n">
-        <v>6431088.884699405</v>
+        <v>6431103</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1337,19 +1252,9 @@
           <t>2019-01-28</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-01-31</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>81754012</v>
+        <v>81754015</v>
       </c>
       <c r="B8" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1420,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469144.8558652933</v>
+        <v>469153</v>
       </c>
       <c r="R8" t="n">
-        <v>6431094.214278215</v>
+        <v>6431105</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,19 +1353,9 @@
           <t>2019-01-28</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2019-01-31</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,37 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>81753922</v>
+        <v>81754016</v>
       </c>
       <c r="B9" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>223246</v>
+        <v>220785</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1536,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469115.1152162474</v>
+        <v>469146</v>
       </c>
       <c r="R9" t="n">
-        <v>6431022.933327258</v>
+        <v>6431083</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,24 +1454,9 @@
           <t>2019-01-28</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2019-01-31</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Öster om E4</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>81754011</v>
+        <v>81754017</v>
       </c>
       <c r="B10" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>469151.7464665595</v>
+        <v>469149</v>
       </c>
       <c r="R10" t="n">
-        <v>6431093.101588313</v>
+        <v>6431089</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1690,19 +1555,9 @@
           <t>2019-01-28</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2019-01-31</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,37 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>81753925</v>
+        <v>81754018</v>
       </c>
       <c r="B11" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223246</v>
+        <v>220785</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1773,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>469132.1914007267</v>
+        <v>469143</v>
       </c>
       <c r="R11" t="n">
-        <v>6431034.984647108</v>
+        <v>6431091</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1806,24 +1656,9 @@
           <t>2019-01-28</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2019-01-31</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Öster om E4</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,37 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>81753923</v>
+        <v>81754019</v>
       </c>
       <c r="B12" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>223246</v>
+        <v>220785</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1894,10 +1724,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>469128.9540238027</v>
+        <v>469152</v>
       </c>
       <c r="R12" t="n">
-        <v>6431028.123397603</v>
+        <v>6431097</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1927,24 +1757,9 @@
           <t>2019-01-28</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2019-01-31</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Öster om E4</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1971,15 +1786,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>81754019</v>
+        <v>81754020</v>
       </c>
       <c r="B13" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,10 +1825,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>469151.7751306365</v>
+        <v>469148</v>
       </c>
       <c r="R13" t="n">
-        <v>6431096.809312133</v>
+        <v>6431097</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2048,19 +1858,9 @@
           <t>2019-01-28</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2019-01-31</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2087,15 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>81754013</v>
+        <v>81754021</v>
       </c>
       <c r="B14" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2131,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>469149.1094655763</v>
+        <v>469164</v>
       </c>
       <c r="R14" t="n">
-        <v>6431095.240801986</v>
+        <v>6431106</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2164,19 +1959,9 @@
           <t>2019-01-28</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2019-01-31</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2203,15 +1988,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>81754018</v>
+        <v>81753922</v>
       </c>
       <c r="B15" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103403</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2219,21 +1999,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220785</v>
+        <v>223246</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2247,10 +2027,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>469143.2392606275</v>
+        <v>469115</v>
       </c>
       <c r="R15" t="n">
-        <v>6431091.048538265</v>
+        <v>6431023</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2280,19 +2060,14 @@
           <t>2019-01-28</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2019-01-31</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Öster om E4</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2319,15 +2094,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>81754020</v>
+        <v>81753923</v>
       </c>
       <c r="B16" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103403</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2335,21 +2105,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220785</v>
+        <v>223246</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2363,10 +2133,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>469148.0603994773</v>
+        <v>469129</v>
       </c>
       <c r="R16" t="n">
-        <v>6431096.838032118</v>
+        <v>6431028</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2396,19 +2166,14 @@
           <t>2019-01-28</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2019-01-31</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Öster om E4</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2432,6 +2197,218 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>81753924</v>
+      </c>
+      <c r="B17" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Norra Boarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>469121</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6431033</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gränna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2019-01-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2019-01-31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Öster om E4</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kajsa Mattsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kajsa Mattsson, Tor Hansson Frank</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>81753925</v>
+      </c>
+      <c r="B18" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Norra Boarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>469132</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6431035</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gränna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2019-01-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2019-01-31</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Öster om E4</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kajsa Mattsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kajsa Mattsson, Tor Hansson Frank</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15760-2026 artfynd.xlsx
+++ b/artfynd/A 15760-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79781427</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81754010</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81754011</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81754012</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81754013</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81754014</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81754015</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81754016</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81754017</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81754018</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81754019</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81754020</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81754021</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2091,6 +2161,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81753922</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2197,6 +2272,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81753923</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2303,6 +2383,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81753924</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2409,8 +2494,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81753925</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>